--- a/xlsx/fluxo_caixa/previsao_latest.xlsx
+++ b/xlsx/fluxo_caixa/previsao_latest.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="115">
   <si>
     <t>Fluxo de Caixa Previsto</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Período de Vencimento</t>
   </si>
   <si>
-    <t>01/09/2027 até 30/09/2027</t>
+    <t>01/12/2026 até 31/12/2026</t>
   </si>
   <si>
     <t>Período de Competência</t>
@@ -93,16 +93,271 @@
     <t>Saldo</t>
   </si>
   <si>
+    <t>Inter</t>
+  </si>
+  <si>
+    <t>01/12/2026</t>
+  </si>
+  <si>
+    <t>PFP-Previsões Financeiras a Pagar</t>
+  </si>
+  <si>
+    <t>12 - 11</t>
+  </si>
+  <si>
+    <t>MARQUES MAIO MARKETING DIGITAL LTDA</t>
+  </si>
+  <si>
+    <t>MACAM EMPREENDIMENTOS C I L ME</t>
+  </si>
+  <si>
+    <t>02/12/2026</t>
+  </si>
+  <si>
+    <t>Vivo</t>
+  </si>
+  <si>
+    <t>04/12/2026</t>
+  </si>
+  <si>
+    <t>DUP-Duplicata de Contrato</t>
+  </si>
+  <si>
+    <t>102301 - 2</t>
+  </si>
+  <si>
+    <t>Thiago Souza Dias Degola</t>
+  </si>
+  <si>
+    <t>05/12/2026</t>
+  </si>
+  <si>
+    <t>100901 - 2</t>
+  </si>
+  <si>
+    <t>Mariana Andrade Derossi</t>
+  </si>
+  <si>
+    <t>1 - 10</t>
+  </si>
+  <si>
+    <t>BIANCA RODRIGUES</t>
+  </si>
+  <si>
+    <t>1 - 9</t>
+  </si>
+  <si>
+    <t>FELIPE DOMINGOS BARBOSA</t>
+  </si>
+  <si>
+    <t>1 - 11</t>
+  </si>
+  <si>
+    <t>DECORA INTERIORES LTDA</t>
+  </si>
+  <si>
+    <t>Hostgator</t>
+  </si>
+  <si>
+    <t>FERNANDA DOCHVAT SILVA</t>
+  </si>
+  <si>
+    <t>Eric Kevin de Souza Serpa</t>
+  </si>
+  <si>
+    <t>3 - 10</t>
+  </si>
+  <si>
+    <t>Promob</t>
+  </si>
+  <si>
+    <t>Danielle Martins da Silva</t>
+  </si>
+  <si>
+    <t>Google</t>
+  </si>
+  <si>
+    <t>Rubens Felipe de Siqueira Costa</t>
+  </si>
+  <si>
+    <t>FERNANDO OLIVEIRA LEITE</t>
+  </si>
+  <si>
+    <t>Carina Pereira</t>
+  </si>
+  <si>
+    <t>SINDICATO DO COM VAREJ E LOJISTA DO COM DE SP - SI</t>
+  </si>
+  <si>
+    <t>THIAGO MAXIMINO DE MENEZES PASSOS</t>
+  </si>
+  <si>
+    <t>Teresinha Elvira Maximino de Menezes</t>
+  </si>
+  <si>
+    <t>SABRINA ALVES DE ABREU BRAUNBECK</t>
+  </si>
+  <si>
+    <t>Jackson Fernando de Araujo</t>
+  </si>
+  <si>
+    <t>D4 sign</t>
+  </si>
+  <si>
+    <t>Sabesp</t>
+  </si>
+  <si>
+    <t>Thais Pereira Pires</t>
+  </si>
+  <si>
+    <t>Denny Lucas do Carmo Pereira</t>
+  </si>
+  <si>
+    <t>GUTEMBERG DIAS GOMES</t>
+  </si>
+  <si>
+    <t>61 - 7</t>
+  </si>
+  <si>
+    <t>Pipefy</t>
+  </si>
+  <si>
+    <t>62 - 6</t>
+  </si>
+  <si>
+    <t>63 - 6</t>
+  </si>
+  <si>
+    <t>67 - 5</t>
+  </si>
+  <si>
+    <t>Mercado livre</t>
+  </si>
+  <si>
+    <t>70 - 3</t>
+  </si>
+  <si>
+    <t>71 - 3</t>
+  </si>
+  <si>
+    <t>72 - 3</t>
+  </si>
+  <si>
+    <t>73 - 3</t>
+  </si>
+  <si>
+    <t>MP  MARKFERRAGENS</t>
+  </si>
+  <si>
+    <t>08/12/2026</t>
+  </si>
+  <si>
+    <t>10/12/2026</t>
+  </si>
+  <si>
+    <t>Roger Duarte Pinheiro Me</t>
+  </si>
+  <si>
+    <t>PREFEITURA SP- ISS</t>
+  </si>
+  <si>
+    <t>12/12/2026</t>
+  </si>
+  <si>
+    <t>2 - 11</t>
+  </si>
+  <si>
+    <t>Enel</t>
+  </si>
+  <si>
+    <t>18/12/2026</t>
+  </si>
+  <si>
+    <t>WEBGIGA SOLUCOES DIGITAIS LTDA</t>
+  </si>
+  <si>
+    <t>12 - 10</t>
+  </si>
+  <si>
+    <t>VERISURE</t>
+  </si>
+  <si>
+    <t>PFR-Previsões Financeiras a Receber</t>
+  </si>
+  <si>
+    <t>MP Interiores e Serv Ltda</t>
+  </si>
+  <si>
+    <t>20/12/2026</t>
+  </si>
+  <si>
+    <t>INSS- Previdenciária</t>
+  </si>
+  <si>
+    <t>IRRF- darf</t>
+  </si>
+  <si>
+    <t>Simples Nacional - DAS</t>
+  </si>
+  <si>
+    <t>CAIXA ECONOMICA FEDERAL- FGTS</t>
+  </si>
+  <si>
+    <t>22/12/2026</t>
+  </si>
+  <si>
+    <t>64 - 6</t>
+  </si>
+  <si>
+    <t>ISO IMPLANTACAO EM SAUDE OCUPACIONAL LTDA</t>
+  </si>
+  <si>
+    <t>25/12/2026</t>
+  </si>
+  <si>
+    <t>68 - 5</t>
+  </si>
+  <si>
+    <t>Luis Carlos Alves de Oliveira</t>
+  </si>
+  <si>
+    <t>26/12/2026</t>
+  </si>
+  <si>
+    <t>EM SOLUCOES INTEGRADAS DE SISTEMAS LTDA ME</t>
+  </si>
+  <si>
+    <t>30/12/2026</t>
+  </si>
+  <si>
+    <t>29001 - 14</t>
+  </si>
+  <si>
+    <t>GABRIEL DE CARVALHO MELLO</t>
+  </si>
+  <si>
+    <t>SEFAZ SP DARE - ICMS</t>
+  </si>
+  <si>
+    <t>Facebook</t>
+  </si>
+  <si>
     <t>Total Geral Crédito</t>
   </si>
   <si>
-    <t>0,00</t>
+    <t>23.747,91</t>
   </si>
   <si>
     <t>Total Geral Débito</t>
   </si>
   <si>
+    <t>102.445,57</t>
+  </si>
+  <si>
     <t>Total Geral Saldo</t>
+  </si>
+  <si>
+    <t>-78.697,66</t>
   </si>
 </sst>
 </file>
@@ -170,7 +425,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A2:H23"/>
+  <dimension ref="A2:H76"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="33.01953125" customWidth="true" bestFit="true"/>
@@ -295,28 +550,1406 @@
         <v>25</v>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B19" t="s" s="1">
+        <v>27</v>
+      </c>
+      <c r="C19" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D19" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="E19" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="F19" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G19" t="n" s="1">
+        <v>808.5</v>
+      </c>
+      <c r="H19" t="n" s="1">
+        <v>-808.5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B20" t="s" s="1">
+        <v>27</v>
+      </c>
+      <c r="C20" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D20" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="E20" t="s" s="1">
+        <v>31</v>
+      </c>
+      <c r="F20" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G20" t="n" s="1">
+        <v>15000.0</v>
+      </c>
+      <c r="H20" t="n" s="1">
+        <v>-15000.0</v>
+      </c>
+    </row>
     <row r="21">
-      <c r="A21" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>27</v>
+      <c r="A21" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B21" t="s" s="1">
+        <v>32</v>
+      </c>
+      <c r="C21" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D21" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="E21" t="s" s="1">
+        <v>33</v>
+      </c>
+      <c r="F21" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G21" t="n" s="1">
+        <v>196.17</v>
+      </c>
+      <c r="H21" t="n" s="1">
+        <v>-196.17</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>27</v>
+      <c r="A22" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B22" t="s" s="1">
+        <v>34</v>
+      </c>
+      <c r="C22" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="D22" t="s" s="1">
+        <v>36</v>
+      </c>
+      <c r="E22" t="s" s="1">
+        <v>37</v>
+      </c>
+      <c r="F22" t="n" s="1">
+        <v>4166.67</v>
+      </c>
+      <c r="G22" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="H22" t="n" s="1">
+        <v>4166.67</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="s">
+      <c r="A23" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B23" t="s" s="1">
+        <v>38</v>
+      </c>
+      <c r="C23" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="D23" t="s" s="1">
+        <v>39</v>
+      </c>
+      <c r="E23" t="s" s="1">
+        <v>40</v>
+      </c>
+      <c r="F23" t="n" s="1">
+        <v>16924.71</v>
+      </c>
+      <c r="G23" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="H23" t="n" s="1">
+        <v>16924.71</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B24" t="s" s="1">
+        <v>38</v>
+      </c>
+      <c r="C24" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D24" t="s" s="1">
+        <v>41</v>
+      </c>
+      <c r="E24" t="s" s="1">
+        <v>42</v>
+      </c>
+      <c r="F24" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G24" t="n" s="1">
+        <v>2536.0</v>
+      </c>
+      <c r="H24" t="n" s="1">
+        <v>-2536.0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B25" t="s" s="1">
+        <v>38</v>
+      </c>
+      <c r="C25" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D25" t="s" s="1">
+        <v>43</v>
+      </c>
+      <c r="E25" t="s" s="1">
+        <v>44</v>
+      </c>
+      <c r="F25" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G25" t="n" s="1">
+        <v>2219.85</v>
+      </c>
+      <c r="H25" t="n" s="1">
+        <v>-2219.85</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B26" t="s" s="1">
+        <v>38</v>
+      </c>
+      <c r="C26" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D26" t="s" s="1">
+        <v>45</v>
+      </c>
+      <c r="E26" t="s" s="1">
+        <v>46</v>
+      </c>
+      <c r="F26" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G26" t="n" s="1">
+        <v>14250.0</v>
+      </c>
+      <c r="H26" t="n" s="1">
+        <v>-14250.0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s" s="1">
+        <v>38</v>
+      </c>
+      <c r="C27" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D27" t="s" s="1">
+        <v>41</v>
+      </c>
+      <c r="E27" t="s" s="1">
+        <v>47</v>
+      </c>
+      <c r="F27" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G27" t="n" s="1">
+        <v>9.99</v>
+      </c>
+      <c r="H27" t="n" s="1">
+        <v>-9.99</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B28" t="s" s="1">
+        <v>38</v>
+      </c>
+      <c r="C28" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D28" t="s" s="1">
+        <v>41</v>
+      </c>
+      <c r="E28" t="s" s="1">
+        <v>48</v>
+      </c>
+      <c r="F28" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G28" t="n" s="1">
+        <v>1000.0</v>
+      </c>
+      <c r="H28" t="n" s="1">
+        <v>-1000.0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B29" t="s" s="1">
+        <v>38</v>
+      </c>
+      <c r="C29" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D29" t="s" s="1">
+        <v>41</v>
+      </c>
+      <c r="E29" t="s" s="1">
+        <v>49</v>
+      </c>
+      <c r="F29" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G29" t="n" s="1">
+        <v>2536.0</v>
+      </c>
+      <c r="H29" t="n" s="1">
+        <v>-2536.0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B30" t="s" s="1">
+        <v>38</v>
+      </c>
+      <c r="C30" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D30" t="s" s="1">
+        <v>50</v>
+      </c>
+      <c r="E30" t="s" s="1">
+        <v>51</v>
+      </c>
+      <c r="F30" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G30" t="n" s="1">
+        <v>1248.82</v>
+      </c>
+      <c r="H30" t="n" s="1">
+        <v>-1248.82</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B31" t="s" s="1">
+        <v>38</v>
+      </c>
+      <c r="C31" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D31" t="s" s="1">
         <v>29</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>27</v>
+      <c r="E31" t="s" s="1">
+        <v>52</v>
+      </c>
+      <c r="F31" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G31" t="n" s="1">
+        <v>1900.0</v>
+      </c>
+      <c r="H31" t="n" s="1">
+        <v>-1900.0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B32" t="s" s="1">
+        <v>38</v>
+      </c>
+      <c r="C32" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D32" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="E32" t="s" s="1">
+        <v>53</v>
+      </c>
+      <c r="F32" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G32" t="n" s="1">
+        <v>14.99</v>
+      </c>
+      <c r="H32" t="n" s="1">
+        <v>-14.99</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B33" t="s" s="1">
+        <v>38</v>
+      </c>
+      <c r="C33" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D33" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="E33" t="s" s="1">
+        <v>54</v>
+      </c>
+      <c r="F33" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G33" t="n" s="1">
+        <v>2120.0</v>
+      </c>
+      <c r="H33" t="n" s="1">
+        <v>-2120.0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B34" t="s" s="1">
+        <v>38</v>
+      </c>
+      <c r="C34" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D34" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="E34" t="s" s="1">
+        <v>55</v>
+      </c>
+      <c r="F34" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G34" t="n" s="1">
+        <v>346.5</v>
+      </c>
+      <c r="H34" t="n" s="1">
+        <v>-346.5</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B35" t="s" s="1">
+        <v>38</v>
+      </c>
+      <c r="C35" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D35" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="E35" t="s" s="1">
+        <v>56</v>
+      </c>
+      <c r="F35" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G35" t="n" s="1">
+        <v>1900.0</v>
+      </c>
+      <c r="H35" t="n" s="1">
+        <v>-1900.0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B36" t="s" s="1">
+        <v>38</v>
+      </c>
+      <c r="C36" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D36" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="E36" t="s" s="1">
+        <v>57</v>
+      </c>
+      <c r="F36" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G36" t="n" s="1">
+        <v>71.17</v>
+      </c>
+      <c r="H36" t="n" s="1">
+        <v>-71.17</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B37" t="s" s="1">
+        <v>38</v>
+      </c>
+      <c r="C37" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D37" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="E37" t="s" s="1">
+        <v>58</v>
+      </c>
+      <c r="F37" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G37" t="n" s="1">
+        <v>1000.0</v>
+      </c>
+      <c r="H37" t="n" s="1">
+        <v>-1000.0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B38" t="s" s="1">
+        <v>38</v>
+      </c>
+      <c r="C38" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D38" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="E38" t="s" s="1">
+        <v>59</v>
+      </c>
+      <c r="F38" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G38" t="n" s="1">
+        <v>1000.0</v>
+      </c>
+      <c r="H38" t="n" s="1">
+        <v>-1000.0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B39" t="s" s="1">
+        <v>38</v>
+      </c>
+      <c r="C39" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D39" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="E39" t="s" s="1">
+        <v>60</v>
+      </c>
+      <c r="F39" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G39" t="n" s="1">
+        <v>4020.07</v>
+      </c>
+      <c r="H39" t="n" s="1">
+        <v>-4020.07</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B40" t="s" s="1">
+        <v>38</v>
+      </c>
+      <c r="C40" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D40" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="E40" t="s" s="1">
+        <v>61</v>
+      </c>
+      <c r="F40" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G40" t="n" s="1">
+        <v>150.0</v>
+      </c>
+      <c r="H40" t="n" s="1">
+        <v>-150.0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B41" t="s" s="1">
+        <v>38</v>
+      </c>
+      <c r="C41" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D41" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="E41" t="s" s="1">
+        <v>62</v>
+      </c>
+      <c r="F41" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G41" t="n" s="1">
+        <v>49.95</v>
+      </c>
+      <c r="H41" t="n" s="1">
+        <v>-49.95</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B42" t="s" s="1">
+        <v>38</v>
+      </c>
+      <c r="C42" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D42" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="E42" t="s" s="1">
+        <v>63</v>
+      </c>
+      <c r="F42" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G42" t="n" s="1">
+        <v>160.0</v>
+      </c>
+      <c r="H42" t="n" s="1">
+        <v>-160.0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B43" t="s" s="1">
+        <v>38</v>
+      </c>
+      <c r="C43" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D43" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="E43" t="s" s="1">
+        <v>64</v>
+      </c>
+      <c r="F43" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G43" t="n" s="1">
+        <v>1800.0</v>
+      </c>
+      <c r="H43" t="n" s="1">
+        <v>-1800.0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B44" t="s" s="1">
+        <v>38</v>
+      </c>
+      <c r="C44" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D44" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="E44" t="s" s="1">
+        <v>65</v>
+      </c>
+      <c r="F44" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G44" t="n" s="1">
+        <v>2479.65</v>
+      </c>
+      <c r="H44" t="n" s="1">
+        <v>-2479.65</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B45" t="s" s="1">
+        <v>38</v>
+      </c>
+      <c r="C45" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D45" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="E45" t="s" s="1">
+        <v>66</v>
+      </c>
+      <c r="F45" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G45" t="n" s="1">
+        <v>6000.0</v>
+      </c>
+      <c r="H45" t="n" s="1">
+        <v>-6000.0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B46" t="s" s="1">
+        <v>38</v>
+      </c>
+      <c r="C46" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D46" t="s" s="1">
+        <v>67</v>
+      </c>
+      <c r="E46" t="s" s="1">
+        <v>68</v>
+      </c>
+      <c r="F46" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G46" t="n" s="1">
+        <v>94.5</v>
+      </c>
+      <c r="H46" t="n" s="1">
+        <v>-94.5</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B47" t="s" s="1">
+        <v>38</v>
+      </c>
+      <c r="C47" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D47" t="s" s="1">
+        <v>69</v>
+      </c>
+      <c r="E47" t="s" s="1">
+        <v>51</v>
+      </c>
+      <c r="F47" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G47" t="n" s="1">
+        <v>293.21</v>
+      </c>
+      <c r="H47" t="n" s="1">
+        <v>-293.21</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B48" t="s" s="1">
+        <v>38</v>
+      </c>
+      <c r="C48" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D48" t="s" s="1">
+        <v>70</v>
+      </c>
+      <c r="E48" t="s" s="1">
+        <v>51</v>
+      </c>
+      <c r="F48" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G48" t="n" s="1">
+        <v>376.44</v>
+      </c>
+      <c r="H48" t="n" s="1">
+        <v>-376.44</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B49" t="s" s="1">
+        <v>38</v>
+      </c>
+      <c r="C49" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D49" t="s" s="1">
+        <v>71</v>
+      </c>
+      <c r="E49" t="s" s="1">
+        <v>72</v>
+      </c>
+      <c r="F49" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G49" t="n" s="1">
+        <v>114.5</v>
+      </c>
+      <c r="H49" t="n" s="1">
+        <v>-114.5</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B50" t="s" s="1">
+        <v>38</v>
+      </c>
+      <c r="C50" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D50" t="s" s="1">
+        <v>73</v>
+      </c>
+      <c r="E50" t="s" s="1">
+        <v>51</v>
+      </c>
+      <c r="F50" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G50" t="n" s="1">
+        <v>188.22</v>
+      </c>
+      <c r="H50" t="n" s="1">
+        <v>-188.22</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B51" t="s" s="1">
+        <v>38</v>
+      </c>
+      <c r="C51" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D51" t="s" s="1">
+        <v>74</v>
+      </c>
+      <c r="E51" t="s" s="1">
+        <v>72</v>
+      </c>
+      <c r="F51" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G51" t="n" s="1">
+        <v>51.58</v>
+      </c>
+      <c r="H51" t="n" s="1">
+        <v>-51.58</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B52" t="s" s="1">
+        <v>38</v>
+      </c>
+      <c r="C52" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D52" t="s" s="1">
+        <v>75</v>
+      </c>
+      <c r="E52" t="s" s="1">
+        <v>72</v>
+      </c>
+      <c r="F52" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G52" t="n" s="1">
+        <v>56.29</v>
+      </c>
+      <c r="H52" t="n" s="1">
+        <v>-56.29</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B53" t="s" s="1">
+        <v>38</v>
+      </c>
+      <c r="C53" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D53" t="s" s="1">
+        <v>76</v>
+      </c>
+      <c r="E53" t="s" s="1">
+        <v>77</v>
+      </c>
+      <c r="F53" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G53" t="n" s="1">
+        <v>100.31</v>
+      </c>
+      <c r="H53" t="n" s="1">
+        <v>-100.31</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B54" t="s" s="1">
+        <v>78</v>
+      </c>
+      <c r="C54" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D54" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="E54" t="s" s="1">
+        <v>51</v>
+      </c>
+      <c r="F54" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G54" t="n" s="1">
+        <v>599.0</v>
+      </c>
+      <c r="H54" t="n" s="1">
+        <v>-599.0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B55" t="s" s="1">
+        <v>79</v>
+      </c>
+      <c r="C55" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D55" t="s" s="1">
+        <v>45</v>
+      </c>
+      <c r="E55" t="s" s="1">
+        <v>80</v>
+      </c>
+      <c r="F55" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G55" t="n" s="1">
+        <v>968.0</v>
+      </c>
+      <c r="H55" t="n" s="1">
+        <v>-968.0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B56" t="s" s="1">
+        <v>79</v>
+      </c>
+      <c r="C56" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D56" t="s" s="1">
+        <v>45</v>
+      </c>
+      <c r="E56" t="s" s="1">
+        <v>81</v>
+      </c>
+      <c r="F56" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G56" t="n" s="1">
+        <v>4.16</v>
+      </c>
+      <c r="H56" t="n" s="1">
+        <v>-4.16</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B57" t="s" s="1">
+        <v>82</v>
+      </c>
+      <c r="C57" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D57" t="s" s="1">
+        <v>83</v>
+      </c>
+      <c r="E57" t="s" s="1">
+        <v>84</v>
+      </c>
+      <c r="F57" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G57" t="n" s="1">
+        <v>750.0</v>
+      </c>
+      <c r="H57" t="n" s="1">
+        <v>-750.0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B58" t="s" s="1">
+        <v>85</v>
+      </c>
+      <c r="C58" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D58" t="s" s="1">
+        <v>41</v>
+      </c>
+      <c r="E58" t="s" s="1">
+        <v>86</v>
+      </c>
+      <c r="F58" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G58" t="n" s="1">
+        <v>4588.5</v>
+      </c>
+      <c r="H58" t="n" s="1">
+        <v>-4588.5</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B59" t="s" s="1">
+        <v>85</v>
+      </c>
+      <c r="C59" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D59" t="s" s="1">
+        <v>87</v>
+      </c>
+      <c r="E59" t="s" s="1">
+        <v>88</v>
+      </c>
+      <c r="F59" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G59" t="n" s="1">
+        <v>239.58</v>
+      </c>
+      <c r="H59" t="n" s="1">
+        <v>-239.58</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B60" t="s" s="1">
+        <v>85</v>
+      </c>
+      <c r="C60" t="s" s="1">
+        <v>89</v>
+      </c>
+      <c r="D60" t="s" s="1">
+        <v>41</v>
+      </c>
+      <c r="E60" t="s" s="1">
+        <v>90</v>
+      </c>
+      <c r="F60" t="n" s="1">
+        <v>840.0</v>
+      </c>
+      <c r="G60" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="H60" t="n" s="1">
+        <v>840.0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B61" t="s" s="1">
+        <v>91</v>
+      </c>
+      <c r="C61" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D61" t="s" s="1">
+        <v>45</v>
+      </c>
+      <c r="E61" t="s" s="1">
+        <v>92</v>
+      </c>
+      <c r="F61" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G61" t="n" s="1">
+        <v>1500.0</v>
+      </c>
+      <c r="H61" t="n" s="1">
+        <v>-1500.0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B62" t="s" s="1">
+        <v>91</v>
+      </c>
+      <c r="C62" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D62" t="s" s="1">
+        <v>45</v>
+      </c>
+      <c r="E62" t="s" s="1">
+        <v>93</v>
+      </c>
+      <c r="F62" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G62" t="n" s="1">
+        <v>4500.0</v>
+      </c>
+      <c r="H62" t="n" s="1">
+        <v>-4500.0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B63" t="s" s="1">
+        <v>91</v>
+      </c>
+      <c r="C63" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D63" t="s" s="1">
+        <v>45</v>
+      </c>
+      <c r="E63" t="s" s="1">
+        <v>94</v>
+      </c>
+      <c r="F63" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G63" t="n" s="1">
+        <v>15000.0</v>
+      </c>
+      <c r="H63" t="n" s="1">
+        <v>-15000.0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B64" t="s" s="1">
+        <v>91</v>
+      </c>
+      <c r="C64" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D64" t="s" s="1">
+        <v>45</v>
+      </c>
+      <c r="E64" t="s" s="1">
+        <v>95</v>
+      </c>
+      <c r="F64" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G64" t="n" s="1">
+        <v>2000.0</v>
+      </c>
+      <c r="H64" t="n" s="1">
+        <v>-2000.0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B65" t="s" s="1">
+        <v>96</v>
+      </c>
+      <c r="C65" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D65" t="s" s="1">
+        <v>97</v>
+      </c>
+      <c r="E65" t="s" s="1">
+        <v>98</v>
+      </c>
+      <c r="F65" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G65" t="n" s="1">
+        <v>146.67</v>
+      </c>
+      <c r="H65" t="n" s="1">
+        <v>-146.67</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B66" t="s" s="1">
+        <v>99</v>
+      </c>
+      <c r="C66" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D66" t="s" s="1">
+        <v>83</v>
+      </c>
+      <c r="E66" t="s" s="1">
+        <v>33</v>
+      </c>
+      <c r="F66" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G66" t="n" s="1">
+        <v>180.06</v>
+      </c>
+      <c r="H66" t="n" s="1">
+        <v>-180.06</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B67" t="s" s="1">
+        <v>99</v>
+      </c>
+      <c r="C67" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D67" t="s" s="1">
+        <v>100</v>
+      </c>
+      <c r="E67" t="s" s="1">
+        <v>101</v>
+      </c>
+      <c r="F67" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G67" t="n" s="1">
+        <v>1925.0</v>
+      </c>
+      <c r="H67" t="n" s="1">
+        <v>-1925.0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B68" t="s" s="1">
+        <v>102</v>
+      </c>
+      <c r="C68" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D68" t="s" s="1">
+        <v>83</v>
+      </c>
+      <c r="E68" t="s" s="1">
+        <v>103</v>
+      </c>
+      <c r="F68" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G68" t="n" s="1">
+        <v>1201.89</v>
+      </c>
+      <c r="H68" t="n" s="1">
+        <v>-1201.89</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B69" t="s" s="1">
+        <v>104</v>
+      </c>
+      <c r="C69" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="D69" t="s" s="1">
+        <v>105</v>
+      </c>
+      <c r="E69" t="s" s="1">
+        <v>106</v>
+      </c>
+      <c r="F69" t="n" s="1">
+        <v>1816.53</v>
+      </c>
+      <c r="G69" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="H69" t="n" s="1">
+        <v>1816.53</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B70" t="s" s="1">
+        <v>104</v>
+      </c>
+      <c r="C70" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D70" t="s" s="1">
+        <v>41</v>
+      </c>
+      <c r="E70" t="s" s="1">
+        <v>107</v>
+      </c>
+      <c r="F70" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G70" t="n" s="1">
+        <v>1000.0</v>
+      </c>
+      <c r="H70" t="n" s="1">
+        <v>-1000.0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B71" t="s" s="1">
+        <v>104</v>
+      </c>
+      <c r="C71" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D71" t="s" s="1">
+        <v>45</v>
+      </c>
+      <c r="E71" t="s" s="1">
+        <v>108</v>
+      </c>
+      <c r="F71" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G71" t="n" s="1">
+        <v>3750.0</v>
+      </c>
+      <c r="H71" t="n" s="1">
+        <v>-3750.0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>114</v>
       </c>
     </row>
   </sheetData>
